--- a/s-s-event-bogor/sessions/clinic/services/services_exercise.xlsx
+++ b/s-s-event-bogor/sessions/clinic/services/services_exercise.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,11 +57,17 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00006100"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -72,6 +78,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003B9C7B"/>
+        <bgColor rgb="003B9C7B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000A5455"/>
+        <bgColor rgb="000A5455"/>
       </patternFill>
     </fill>
     <fill>
@@ -107,17 +125,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -486,11 +514,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -503,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>4 services: fish provisioning, carbon, recreation, coastal protection</t>
+          <t>Part A: Physical quantification | Part B: Monetary valuation</t>
         </is>
       </c>
     </row>
@@ -550,253 +579,391 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Reef fish catch</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>180,000 kg/yr</t>
-        </is>
-      </c>
-    </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Average fish price</t>
+          <t>Reef fish catch</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>USD 3.50/kg</t>
+          <t>180,000 kg/yr</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Total fishing costs</t>
+          <t>Average fish price</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>USD 420,000/yr</t>
+          <t>USD 3.50/kg</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Mangrove NCP rate</t>
+          <t>Total fishing costs</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3.7 Mg CO2/ha/yr</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Seagrass NCP rate</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>1.3 Mg CO2/ha/yr</t>
+          <t>USD 420,000/yr</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Social cost of carbon</t>
+          <t>Mangrove NCP rate</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>USD 51/Mg CO2</t>
+          <t>3.7 Mg CO2/ha/yr</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Reef visitors</t>
+          <t>Seagrass NCP rate</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>15,000/yr</t>
+          <t>1.3 Mg CO2/ha/yr</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Reef spending per visitor</t>
+          <t>Social cost of carbon</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>USD 85</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Protected coastline</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>12,000 m</t>
+          <t>USD 51/Mg CO2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Seawall replacement cost</t>
+          <t>Reef visitors</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>USD 5,000/m</t>
+          <t>15,000/yr</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>Reef spending per visitor</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>USD 85</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Protected coastline</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>12,000 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Seawall cost</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>USD 5,000/m</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
           <t>Seawall lifespan</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>50 years</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Part 1: Fish Provisioning</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Gross revenue</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Total costs</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Resource rent</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n"/>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>PART A: Physical Quantification</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Part 2: Carbon Sequestration</t>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>A1: Carbon (Mg CO2/yr)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Mangrove physical (Mg CO2/yr)</t>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Mangrove: 350 x 3.7 =</t>
         </is>
       </c>
       <c r="B27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Mangrove value (USD/yr)</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Seagrass: 800 x 1.3 =</t>
         </is>
       </c>
       <c r="B28" s="6" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Seagrass physical (Mg CO2/yr)</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Total carbon:</t>
         </is>
       </c>
       <c r="B29" s="6" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Seagrass value (USD/yr)</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Total carbon value (USD/yr)</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n"/>
+          <t>Physical Supply Table (Part A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Part 3: Recreation</t>
-        </is>
-      </c>
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Carbon sequestration</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Mg CO2/yr</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Recreation value (USD/yr)</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n"/>
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Fish provisioning</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>kg/yr</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Coastal protection</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Part 4: Coastal Protection</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Total replacement cost (USD)</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Annualized value (USD/yr)</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="n"/>
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>visitors/yr</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>PART B: Monetary Valuation</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>B1: Fish revenue (180,000 x 3.50) =</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>B1: Resource rent (revenue - 420,000) =</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>B2: Carbon value (total Mg CO2 x 51) =</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>B3: Recreation (15,000 x 85) =</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>B4: Coastal total (12,000 x 5,000) =</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>B4: Annualized (total / 50) =</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Monetary Supply Table (Part B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Fish provisioning</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>Resource rent</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>Carbon sequestration</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>SCC</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>Direct expenditure</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>Coastal protection</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>Replacement cost</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr"/>
+      <c r="C56" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -810,11 +977,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -825,117 +992,197 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Fish: Gross revenue</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n">
-        <v>630000</v>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Part A: Physical Supply</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Fish: Resource rent</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>210000</v>
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Carbon (mangrove)</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>1,295 Mg CO2/yr</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Mangrove carbon (Mg CO2/yr)</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>1295</v>
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Carbon (seagrass)</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>1,040 Mg CO2/yr</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Mangrove carbon value (USD/yr)</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>66045</v>
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Carbon total</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>2,335 Mg CO2/yr</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Seagrass carbon (Mg CO2/yr)</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>1040</v>
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Fish provisioning</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>180,000 kg/yr</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Seagrass carbon value (USD/yr)</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n">
-        <v>53040</v>
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Coastal protection</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>12,000 m</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Total carbon value (USD/yr)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n">
-        <v>119085</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Recreation value (USD/yr)</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>1275000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Coastal protection total (USD)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>60000000</v>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>15,000 visitors/yr</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Coastal protection annualized (USD/yr)</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>1200000</v>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Part B: Monetary Valuation</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Fish: gross revenue</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>USD 630,000</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL ecosystem services (USD/yr)</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>2804085</v>
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Fish: resource rent</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>USD 210,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Carbon: mangrove</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>USD 66,045</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Carbon: seagrass</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>USD 53,040</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Carbon: total</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>USD 119,085</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>USD 1,275,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Coastal: total replacement</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>USD 60,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Coastal: annualized</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>USD 1,200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL (all services)</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>USD 2,804,085</t>
+        </is>
       </c>
     </row>
   </sheetData>
